--- a/data/electric_fifteen.xlsx
+++ b/data/electric_fifteen.xlsx
@@ -1281,30 +1281,30 @@
     <row r="3" spans="1:17">
       <c r="A3" s="1"/>
       <c r="B3" s="1">
-        <v>0.493604393423098</v>
+        <v>0.516040956760512</v>
       </c>
       <c r="C3" s="1">
-        <v>0.616781685248288</v>
+        <v>0.644817216395937</v>
       </c>
       <c r="D3" s="1">
-        <v>0.512345915903</v>
+        <v>0.535634366625864</v>
       </c>
       <c r="E3" s="1">
-        <v>0.646891851655805</v>
+        <v>0.676296026731068</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1">
-        <v>0.590736915806056</v>
+        <v>0.557918198261275</v>
       </c>
       <c r="I3" s="1">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J3" s="1">
-        <v>0.464519516891301</v>
+        <v>0.438712877064006</v>
       </c>
       <c r="K3" s="1">
-        <v>0.509606161386312</v>
+        <v>0.481294707975961</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -1324,30 +1324,30 @@
     <row r="4" spans="1:17">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
-        <v>0.477883349323453</v>
+        <v>0.499605319747246</v>
       </c>
       <c r="C4" s="1">
-        <v>0.60726899791577</v>
+        <v>0.634872134184669</v>
       </c>
       <c r="D4" s="1">
-        <v>0.506123002613557</v>
+        <v>0.529128593641446</v>
       </c>
       <c r="E4" s="1">
-        <v>0.635348529460416</v>
+        <v>0.664228008072253</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1">
-        <v>0.5758839488885</v>
+        <v>0.543890396172472</v>
       </c>
       <c r="I4" s="1">
-        <v>0.865699282338526</v>
+        <v>0.817604877764163</v>
       </c>
       <c r="J4" s="1">
-        <v>0.483373884123928</v>
+        <v>0.456519779450376</v>
       </c>
       <c r="K4" s="1">
-        <v>0.645317696481709</v>
+        <v>0.609466713343836</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -1367,30 +1367,30 @@
     <row r="5" spans="1:17">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
-        <v>0.460590200813842</v>
+        <v>0.481526119032653</v>
       </c>
       <c r="C5" s="1">
-        <v>0.741254507559467</v>
+        <v>0.774947894266716</v>
       </c>
       <c r="D5" s="1">
-        <v>0.61318622423661</v>
+        <v>0.641058325338274</v>
       </c>
       <c r="E5" s="1">
-        <v>0.766357230290799</v>
+        <v>0.801191649849472</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1">
-        <v>0.547078592683354</v>
+        <v>0.516685337534278</v>
       </c>
       <c r="I5" s="1">
-        <v>0.69883773849116</v>
+        <v>0.660013419686096</v>
       </c>
       <c r="J5" s="1">
-        <v>0.463934010152284</v>
+        <v>0.438159898477157</v>
       </c>
       <c r="K5" s="1">
-        <v>0.469434622790128</v>
+        <v>0.443354921524009</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -1410,30 +1410,30 @@
     <row r="6" spans="1:17">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
-        <v>0.474739140503524</v>
+        <v>0.496318192344593</v>
       </c>
       <c r="C6" s="1">
-        <v>0.706915671419592</v>
+        <v>0.739048201938664</v>
       </c>
       <c r="D6" s="1">
-        <v>0.585798127501903</v>
+        <v>0.612425315115626</v>
       </c>
       <c r="E6" s="1">
-        <v>0.73142157673603</v>
+        <v>0.764668012042213</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1">
-        <v>0.503420269560651</v>
+        <v>0.475452476807282</v>
       </c>
       <c r="I6" s="1">
-        <v>0.773803605811307</v>
+        <v>0.730814516599568</v>
       </c>
       <c r="J6" s="1">
-        <v>0.505108524417994</v>
+        <v>0.477046939728105</v>
       </c>
       <c r="K6" s="1">
-        <v>0.551353054437248</v>
+        <v>0.520722329190735</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -1453,30 +1453,30 @@
     <row r="7" spans="1:17">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
-        <v>0.476311244913488</v>
+        <v>0.497961756045919</v>
       </c>
       <c r="C7" s="1">
-        <v>0.764916134581665</v>
+        <v>0.799685049789922</v>
       </c>
       <c r="D7" s="1">
-        <v>0.631862242366097</v>
+        <v>0.660583253382737</v>
       </c>
       <c r="E7" s="1">
-        <v>0.785411718000463</v>
+        <v>0.821112250636848</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1">
-        <v>0.528174339226326</v>
+        <v>0.498831320380419</v>
       </c>
       <c r="I7" s="1">
-        <v>0.676107999299842</v>
+        <v>0.638546443783184</v>
       </c>
       <c r="J7" s="1">
-        <v>0.429712060213548</v>
+        <v>0.405839167979462</v>
       </c>
       <c r="K7" s="1">
-        <v>0.503698582180991</v>
+        <v>0.47571532761538</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -1496,30 +1496,30 @@
     <row r="8" spans="1:17">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
-        <v>0.532266516690377</v>
+        <v>0.556460449267212</v>
       </c>
       <c r="C8" s="1">
-        <v>0.807312005822609</v>
+        <v>0.844008006087273</v>
       </c>
       <c r="D8" s="1">
-        <v>0.666725113309294</v>
+        <v>0.697030800277898</v>
       </c>
       <c r="E8" s="1">
-        <v>0.824212128229729</v>
+        <v>0.861676315876534</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1">
-        <v>0.521423945387712</v>
+        <v>0.492455948421728</v>
       </c>
       <c r="I8" s="1">
-        <v>0.587531069490635</v>
+        <v>0.554890454518933</v>
       </c>
       <c r="J8" s="1">
-        <v>0.510257307894277</v>
+        <v>0.481909679677928</v>
       </c>
       <c r="K8" s="1">
-        <v>0.484311220024505</v>
+        <v>0.457405041134255</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="O8" s="1">
-        <v>0.0418911085747067</v>
+        <v>0.0395638247650008</v>
       </c>
       <c r="P8" s="1">
         <v>0</v>
@@ -1539,514 +1539,514 @@
     <row r="9" spans="1:17">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
-        <v>0.55805339597049</v>
+        <v>0.583419459423694</v>
       </c>
       <c r="C9" s="1">
-        <v>0.834823832996989</v>
+        <v>0.872770370860488</v>
       </c>
       <c r="D9" s="1">
-        <v>0.671703443940848</v>
+        <v>0.702235418665432</v>
       </c>
       <c r="E9" s="1">
-        <v>0.854526085949647</v>
+        <v>0.89336818076554</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1">
-        <v>0.552455802555575</v>
+        <v>0.521763813524709</v>
       </c>
       <c r="I9" s="1">
-        <v>0.54502538071066</v>
+        <v>0.514746192893401</v>
       </c>
       <c r="J9" s="1">
-        <v>0.611552599334851</v>
+        <v>0.577577454927359</v>
       </c>
       <c r="K9" s="1">
-        <v>0.492915280938211</v>
+        <v>0.465531098663866</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1">
-        <v>0.0915430169534067</v>
+        <v>0.0864572937893286</v>
       </c>
       <c r="O9" s="1">
-        <v>0.131933596667881</v>
+        <v>0.124603952408555</v>
       </c>
       <c r="P9" s="1">
-        <v>0.0689544104552978</v>
+        <v>0.065123609874448</v>
       </c>
       <c r="Q9" s="1">
-        <v>0.0583915477976109</v>
+        <v>0.0551475729199658</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
-        <v>0.573774440070136</v>
+        <v>0.59985509643696</v>
       </c>
       <c r="C10" s="1">
-        <v>0.90548119231151</v>
+        <v>0.94663942832567</v>
       </c>
       <c r="D10" s="1">
-        <v>0.729995037549212</v>
+        <v>0.763176630165085</v>
       </c>
       <c r="E10" s="1">
-        <v>0.916507757964734</v>
+        <v>0.958167201508586</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1">
-        <v>0.557255382461053</v>
+        <v>0.526296750102106</v>
       </c>
       <c r="I10" s="1">
-        <v>0.537518816733765</v>
+        <v>0.507656660248556</v>
       </c>
       <c r="J10" s="1">
-        <v>0.57021529844215</v>
+        <v>0.538536670750919</v>
       </c>
       <c r="K10" s="1">
-        <v>0.551037983546298</v>
+        <v>0.52042476223817</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1">
-        <v>0.164434298826946</v>
+        <v>0.155299060003227</v>
       </c>
       <c r="O10" s="1">
-        <v>0.28213707340102</v>
+        <v>0.266462791545407</v>
       </c>
       <c r="P10" s="1">
-        <v>0.152279477235107</v>
+        <v>0.143819506277601</v>
       </c>
       <c r="Q10" s="1">
-        <v>0.100815102096916</v>
+        <v>0.0952142630915314</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
-        <v>0.587901544976346</v>
+        <v>0.61462434247527</v>
       </c>
       <c r="C11" s="1">
-        <v>1.01033182254276</v>
+        <v>1.0562559962947</v>
       </c>
       <c r="D11" s="1">
-        <v>0.815121580044331</v>
+        <v>0.852172560955437</v>
       </c>
       <c r="E11" s="1">
-        <v>1.01648923148179</v>
+        <v>1.06269328745823</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1">
-        <v>0.613020304568528</v>
+        <v>0.578963620981388</v>
       </c>
       <c r="I11" s="1">
-        <v>0.491799404866095</v>
+        <v>0.464477215706868</v>
       </c>
       <c r="J11" s="1">
-        <v>0.573229476632242</v>
+        <v>0.541383394597117</v>
       </c>
       <c r="K11" s="1">
-        <v>0.541068615438474</v>
+        <v>0.511009247914114</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1">
-        <v>0.22638624126783</v>
+        <v>0.213809227864062</v>
       </c>
       <c r="O11" s="1">
-        <v>0.428070227858087</v>
+        <v>0.404288548532637</v>
       </c>
       <c r="P11" s="1">
-        <v>0.212080123819028</v>
+        <v>0.200297894717971</v>
       </c>
       <c r="Q11" s="1">
-        <v>0.15163946671766</v>
+        <v>0.143215051900013</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
-        <v>0.620493598438482</v>
+        <v>0.648697852912958</v>
       </c>
       <c r="C12" s="1">
-        <v>0.965519568597612</v>
+        <v>1.00940682171568</v>
       </c>
       <c r="D12" s="1">
-        <v>0.778773943825057</v>
+        <v>0.814172759453469</v>
       </c>
       <c r="E12" s="1">
-        <v>0.972841499321799</v>
+        <v>1.01706156747279</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1">
-        <v>0.575988972518817</v>
+        <v>0.543989585156661</v>
       </c>
       <c r="I12" s="1">
-        <v>0.599175564502013</v>
+        <v>0.56588803314079</v>
       </c>
       <c r="J12" s="1">
-        <v>0.597736740766673</v>
+        <v>0.564529144057413</v>
       </c>
       <c r="K12" s="1">
-        <v>0.517719236828287</v>
+        <v>0.488957057004493</v>
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1">
-        <v>0.338802206273418</v>
+        <v>0.31997986148045</v>
       </c>
       <c r="O12" s="1">
-        <v>0.469197626403571</v>
+        <v>0.443131091603373</v>
       </c>
       <c r="P12" s="1">
-        <v>0.326249394948041</v>
+        <v>0.308124428562038</v>
       </c>
       <c r="Q12" s="1">
-        <v>0.239917892208126</v>
+        <v>0.226589120418786</v>
       </c>
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
-        <v>0.649708538723658</v>
+        <v>0.679240745029278</v>
       </c>
       <c r="C13" s="1">
-        <v>1.03429185827241</v>
+        <v>1.08130512455751</v>
       </c>
       <c r="D13" s="1">
-        <v>0.835813676514375</v>
+        <v>0.873805207265028</v>
       </c>
       <c r="E13" s="1">
-        <v>1.04229794554537</v>
+        <v>1.08967512488834</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1">
-        <v>0.706937685979345</v>
+        <v>0.667663370091604</v>
       </c>
       <c r="I13" s="1">
-        <v>0.625420969718187</v>
+        <v>0.590675360289398</v>
       </c>
       <c r="J13" s="1">
-        <v>0.561458953264485</v>
+        <v>0.530266789194236</v>
       </c>
       <c r="K13" s="1">
-        <v>0.444688429896726</v>
+        <v>0.419983517124686</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1">
-        <v>0.474656539640614</v>
+        <v>0.448286731882802</v>
       </c>
       <c r="O13" s="1">
-        <v>0.590627521049832</v>
+        <v>0.557814880991508</v>
       </c>
       <c r="P13" s="1">
-        <v>0.469670911492103</v>
+        <v>0.443578083075875</v>
       </c>
       <c r="Q13" s="1">
-        <v>0.354124811014635</v>
+        <v>0.334451210402711</v>
       </c>
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
-        <v>0.674753035365733</v>
+        <v>0.705423627882357</v>
       </c>
       <c r="C14" s="1">
-        <v>1.12911304462898</v>
+        <v>1.18043636483938</v>
       </c>
       <c r="D14" s="1">
-        <v>0.964274985939723</v>
+        <v>1.0081056671188</v>
       </c>
       <c r="E14" s="1">
-        <v>1.12611440103219</v>
+        <v>1.17730141926093</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1">
-        <v>0.685363206721513</v>
+        <v>0.647287473014762</v>
       </c>
       <c r="I14" s="1">
-        <v>0.546101872921408</v>
+        <v>0.515762879981329</v>
       </c>
       <c r="J14" s="1">
-        <v>0.61492385786802</v>
+        <v>0.580761421319797</v>
       </c>
       <c r="K14" s="1">
-        <v>0.483085069140557</v>
+        <v>0.456247009743859</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1">
-        <v>0.6522729038311</v>
+        <v>0.616035520284927</v>
       </c>
       <c r="O14" s="1">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="P14" s="1">
-        <v>0.672075582194441</v>
+        <v>0.634738049850305</v>
       </c>
       <c r="Q14" s="1">
-        <v>0.552877656999779</v>
+        <v>0.522162231610902</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
-        <v>0.675837496278162</v>
+        <v>0.706557382472624</v>
       </c>
       <c r="C15" s="1">
-        <v>1.00347570053264</v>
+        <v>1.04908823237503</v>
       </c>
       <c r="D15" s="1">
-        <v>0.841024911502961</v>
+        <v>0.879253316571277</v>
       </c>
       <c r="E15" s="1">
-        <v>0.988562543421444</v>
+        <v>1.03349720448606</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1">
-        <v>0.617528443899877</v>
+        <v>0.583221308127662</v>
       </c>
       <c r="I15" s="1">
-        <v>0.393137580955715</v>
+        <v>0.371296604235953</v>
       </c>
       <c r="J15" s="1">
-        <v>0.587720112025206</v>
+        <v>0.555068994690472</v>
       </c>
       <c r="K15" s="1">
-        <v>0.360354454752319</v>
+        <v>0.340334762821635</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1">
-        <v>0.499224338327129</v>
+        <v>0.47148965286451</v>
       </c>
       <c r="O15" s="1">
-        <v>0.667971985347285</v>
+        <v>0.630862430605769</v>
       </c>
       <c r="P15" s="1">
-        <v>0.47750700665109</v>
+        <v>0.450978839614918</v>
       </c>
       <c r="Q15" s="1">
-        <v>0.459000484041568</v>
+        <v>0.433500457150369</v>
       </c>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
-        <v>0.614612763423429</v>
+        <v>0.642549707215403</v>
       </c>
       <c r="C16" s="1">
-        <v>0.982223177953486</v>
+        <v>1.02686968604228</v>
       </c>
       <c r="D16" s="1">
-        <v>0.826235484831442</v>
+        <v>0.863791643232872</v>
       </c>
       <c r="E16" s="1">
-        <v>0.96827075131505</v>
+        <v>1.01228305819301</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1">
-        <v>0.790208296866795</v>
+        <v>0.746307835929751</v>
       </c>
       <c r="I16" s="1">
-        <v>0.479062664099422</v>
+        <v>0.452448071649454</v>
       </c>
       <c r="J16" s="1">
-        <v>0.597395413968142</v>
+        <v>0.564206779858801</v>
       </c>
       <c r="K16" s="1">
-        <v>0.558618064064414</v>
+        <v>0.527583727171947</v>
       </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1">
-        <v>0.396887194411412</v>
+        <v>0.374837905833</v>
       </c>
       <c r="O16" s="1">
-        <v>0.61354957840577</v>
+        <v>0.579463490716561</v>
       </c>
       <c r="P16" s="1">
-        <v>0.393186965537435</v>
+        <v>0.3713432452298</v>
       </c>
       <c r="Q16" s="1">
-        <v>0.338796828033775</v>
+        <v>0.319974782031899</v>
       </c>
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
-        <v>0.594451980017865</v>
+        <v>0.621472524564132</v>
       </c>
       <c r="C17" s="1">
-        <v>0.942716776391968</v>
+        <v>0.985567538955239</v>
       </c>
       <c r="D17" s="1">
-        <v>0.739267542263539</v>
+        <v>0.772870612366427</v>
       </c>
       <c r="E17" s="1">
-        <v>0.930482019386642</v>
+        <v>0.972776656631489</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1">
-        <v>0.604316471206021</v>
+        <v>0.570743333916798</v>
       </c>
       <c r="I17" s="1">
-        <v>0.536676002100473</v>
+        <v>0.506860668650446</v>
       </c>
       <c r="J17" s="1">
-        <v>0.586052861893926</v>
+        <v>0.553494369566486</v>
       </c>
       <c r="K17" s="1">
-        <v>0.637834762821635</v>
+        <v>0.602399498220433</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1">
-        <v>0.281050668993253</v>
+        <v>0.265436742938073</v>
       </c>
       <c r="O17" s="1">
-        <v>0.44749642944646</v>
+        <v>0.422635516699434</v>
       </c>
       <c r="P17" s="1">
-        <v>0.273827693153501</v>
+        <v>0.258615043533862</v>
       </c>
       <c r="Q17" s="1">
-        <v>0.219754871788743</v>
+        <v>0.207546267800479</v>
       </c>
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
-        <v>0.618317398352466</v>
+        <v>0.646422734641214</v>
       </c>
       <c r="C18" s="1">
-        <v>0.824481423892546</v>
+        <v>0.861957852251298</v>
       </c>
       <c r="D18" s="1">
-        <v>0.645559929864029</v>
+        <v>0.674903563039667</v>
       </c>
       <c r="E18" s="1">
-        <v>0.822028649882556</v>
+        <v>0.859393588513581</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1">
-        <v>0.632029581655872</v>
+        <v>0.596916827119435</v>
       </c>
       <c r="I18" s="1">
-        <v>0.615598634692806</v>
+        <v>0.581398710543205</v>
       </c>
       <c r="J18" s="1">
-        <v>0.543439523892876</v>
+        <v>0.513248439232161</v>
       </c>
       <c r="K18" s="1">
-        <v>0.658962891650622</v>
+        <v>0.622353842114476</v>
       </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1">
-        <v>0.220787493800085</v>
+        <v>0.208521521922302</v>
       </c>
       <c r="O18" s="1">
-        <v>0.416646846857614</v>
+        <v>0.393499799809969</v>
       </c>
       <c r="P18" s="1">
-        <v>0.256235471283188</v>
+        <v>0.242000167323011</v>
       </c>
       <c r="Q18" s="1">
-        <v>0.10388607693273</v>
+        <v>0.098114628214245</v>
       </c>
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
-        <v>0.602072319449499</v>
+        <v>0.629439243060839</v>
       </c>
       <c r="C19" s="1">
-        <v>0.866607999470672</v>
+        <v>0.905999272173884</v>
       </c>
       <c r="D19" s="1">
-        <v>0.677518774605485</v>
+        <v>0.708315082542098</v>
       </c>
       <c r="E19" s="1">
-        <v>0.819845171535382</v>
+        <v>0.857110861150627</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1">
-        <v>0.581799404866095</v>
+        <v>0.549477215706867</v>
       </c>
       <c r="I19" s="1">
-        <v>0.649334850341327</v>
+        <v>0.613260691989031</v>
       </c>
       <c r="J19" s="1">
-        <v>0.545067390162786</v>
+        <v>0.514785868487076</v>
       </c>
       <c r="K19" s="1">
-        <v>0.690105023630317</v>
+        <v>0.651765855650855</v>
       </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1">
-        <v>0.10589753855899</v>
+        <v>0.100014341972379</v>
       </c>
       <c r="O19" s="1">
-        <v>0.252712724317411</v>
+        <v>0.238673128522</v>
       </c>
       <c r="P19" s="1">
-        <v>0.123183200769686</v>
+        <v>0.116339689615815</v>
       </c>
       <c r="Q19" s="1">
-        <v>0.0537985311429955</v>
+        <v>0.0508097238572735</v>
       </c>
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
-        <v>0.595550997452609</v>
+        <v>0.622621497336818</v>
       </c>
       <c r="C20" s="1">
-        <v>0.890662652595362</v>
+        <v>0.931147318622424</v>
       </c>
       <c r="D20" s="1">
-        <v>0.701580705991332</v>
+        <v>0.733470738081847</v>
       </c>
       <c r="E20" s="1">
-        <v>0.840588215833527</v>
+        <v>0.878796771098687</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1">
-        <v>0.568915631016979</v>
+        <v>0.537309207071591</v>
       </c>
       <c r="I20" s="1">
-        <v>0.585900577629967</v>
+        <v>0.553350545539413</v>
       </c>
       <c r="J20" s="1">
-        <v>0.599262208997025</v>
+        <v>0.565969864052746</v>
       </c>
       <c r="K20" s="1">
-        <v>0.497630841939436</v>
+        <v>0.469984684053912</v>
       </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1">
-        <v>0.0806520816775327</v>
+        <v>0.0761714104732253</v>
       </c>
       <c r="O20" s="1">
-        <v>0.0853472848853539</v>
+        <v>0.0806057690583898</v>
       </c>
       <c r="P20" s="1">
-        <v>0.0769733657621265</v>
+        <v>0.0726970676642305</v>
       </c>
       <c r="Q20" s="1">
         <v>0</v>
@@ -2055,30 +2055,30 @@
     <row r="21" spans="1:17">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
-        <v>0.59467760611374</v>
+        <v>0.621708406391637</v>
       </c>
       <c r="C21" s="1">
-        <v>0.821897641181725</v>
+        <v>0.859256624871803</v>
       </c>
       <c r="D21" s="1">
-        <v>0.675662818010388</v>
+        <v>0.706374764283587</v>
       </c>
       <c r="E21" s="1">
-        <v>0.826395606576902</v>
+        <v>0.863959043239488</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1">
-        <v>0.613692455802556</v>
+        <v>0.579598430480191</v>
       </c>
       <c r="I21" s="1">
-        <v>0.554826711009977</v>
+        <v>0.524003004842756</v>
       </c>
       <c r="J21" s="1">
-        <v>0.459688429896727</v>
+        <v>0.434150183791353</v>
       </c>
       <c r="K21" s="1">
-        <v>0.563462279012777</v>
+        <v>0.532158819067623</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -2086,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="1">
-        <v>0.00978839614918044</v>
+        <v>0.00924459636311486</v>
       </c>
       <c r="P21" s="1">
         <v>0</v>
@@ -2098,30 +2098,30 @@
     <row r="22" spans="1:17">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
-        <v>0.612385615509313</v>
+        <v>0.64022132530519</v>
       </c>
       <c r="C22" s="1">
-        <v>0.906398253217323</v>
+        <v>0.94759817381811</v>
       </c>
       <c r="D22" s="1">
-        <v>0.742666490223971</v>
+        <v>0.776424057961425</v>
       </c>
       <c r="E22" s="1">
-        <v>0.900633870380785</v>
+        <v>0.941571773579912</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1">
-        <v>0.624890600385087</v>
+        <v>0.590174455919249</v>
       </c>
       <c r="I22" s="1">
-        <v>0.597731489585157</v>
+        <v>0.564524184608204</v>
       </c>
       <c r="J22" s="1">
-        <v>0.504152809382111</v>
+        <v>0.476144319971994</v>
       </c>
       <c r="K22" s="1">
-        <v>0.506788902503063</v>
+        <v>0.478633963475115</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -2141,30 +2141,30 @@
     <row r="23" spans="1:17">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
-        <v>0.610405928474542</v>
+        <v>0.638151652496112</v>
       </c>
       <c r="C23" s="1">
-        <v>0.857051642571211</v>
+        <v>0.896008535415357</v>
       </c>
       <c r="D23" s="1">
-        <v>0.703625897376518</v>
+        <v>0.735608892711814</v>
       </c>
       <c r="E23" s="1">
-        <v>0.858056042610911</v>
+        <v>0.897058590002316</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1">
-        <v>0.66649046035358</v>
+        <v>0.629463212556159</v>
       </c>
       <c r="I23" s="1">
-        <v>0.588366007351654</v>
+        <v>0.555679006943229</v>
       </c>
       <c r="J23" s="1">
-        <v>0.533793103448276</v>
+        <v>0.504137931034483</v>
       </c>
       <c r="K23" s="1">
-        <v>0.511969193068441</v>
+        <v>0.483526460120194</v>
       </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -2184,30 +2184,30 @@
     <row r="24" spans="1:17">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
-        <v>0.587632249313528</v>
+        <v>0.614342806100507</v>
       </c>
       <c r="C24" s="1">
-        <v>0.797864822840507</v>
+        <v>0.834131405696894</v>
       </c>
       <c r="D24" s="1">
-        <v>0.657117808581731</v>
+        <v>0.686986799880901</v>
       </c>
       <c r="E24" s="1">
-        <v>0.793010222648625</v>
+        <v>0.829056141859926</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1">
-        <v>0.605474356730264</v>
+        <v>0.571836892467472</v>
       </c>
       <c r="I24" s="1">
-        <v>0.551408191843164</v>
+        <v>0.520774403407433</v>
       </c>
       <c r="J24" s="1">
-        <v>0.434537896026606</v>
+        <v>0.410396901802906</v>
       </c>
       <c r="K24" s="1">
-        <v>0.470222300017504</v>
+        <v>0.44409883890542</v>
       </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -2227,30 +2227,30 @@
     <row r="25" spans="1:17">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
-        <v>0.572777318291594</v>
+        <v>0.598812650941212</v>
       </c>
       <c r="C25" s="1">
-        <v>0.724580011248222</v>
+        <v>0.757515466304959</v>
       </c>
       <c r="D25" s="1">
-        <v>0.597494293181592</v>
+        <v>0.624653124689847</v>
       </c>
       <c r="E25" s="1">
-        <v>0.729238098388857</v>
+        <v>0.76238528467926</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1">
-        <v>0.614020654647295</v>
+        <v>0.579908396055779</v>
       </c>
       <c r="I25" s="1">
-        <v>0.517251881673376</v>
+        <v>0.488515666024855</v>
       </c>
       <c r="J25" s="1">
-        <v>0.414328723962891</v>
+        <v>0.391310461520508</v>
       </c>
       <c r="K25" s="1">
-        <v>0.544263959390863</v>
+        <v>0.514027072758037</v>
       </c>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -2270,30 +2270,30 @@
     <row r="26" spans="1:17">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
-        <v>0.523263307638866</v>
+        <v>0.547048003440633</v>
       </c>
       <c r="C26" s="1">
-        <v>0.641345816653985</v>
+        <v>0.670497899229166</v>
       </c>
       <c r="D26" s="1">
-        <v>0.528379925232408</v>
+        <v>0.552397194561153</v>
       </c>
       <c r="E26" s="1">
-        <v>0.649541138717041</v>
+        <v>0.679065735931452</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1">
-        <v>0.619053912130229</v>
+        <v>0.584662028122994</v>
       </c>
       <c r="I26" s="1">
-        <v>0.605920707159111</v>
+        <v>0.572258445650272</v>
       </c>
       <c r="J26" s="1">
-        <v>0.403997024330474</v>
+        <v>0.381552745201004</v>
       </c>
       <c r="K26" s="1">
-        <v>0.598217223875372</v>
+        <v>0.564982933660074</v>
       </c>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
